--- a/architecture/DevOpsBuildDeployAndEnvironmentManagement/deployment_facts_inventory_2026-07-09.xlsx
+++ b/architecture/DevOpsBuildDeployAndEnvironmentManagement/deployment_facts_inventory_2026-07-09.xlsx
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/pyproject.toml</t>
+          <t>ChatHealthyLib/pyproject.toml</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/__init__.py</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/__init__.py</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/auth_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/auth_token.py</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/nonce.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/nonce.py</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/session_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/session_token.py</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/exceptions.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/exceptions.py</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/geo_extractor.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/geo_extractor.py</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/llm.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/llm.py</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/logging_service.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/logging_service.py</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/mongo_utilities.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/mongo_utilities.py</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/provider_embedding.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/provider_embedding.py</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/runtime_data_collections.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/runtime_data_collections.py</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/user/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/user/__init__.py</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_llm_facade.py</t>
+          <t>ChatHealthyLib/tests/test_llm_facade.py</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_logging_service_levels.py</t>
+          <t>ChatHealthyLib/tests/test_logging_service_levels.py</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_mongo_utilities_batch_size.py</t>
+          <t>ChatHealthyLib/tests/test_mongo_utilities_batch_size.py</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib</t>
+          <t>ChatHealthyLib</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib</t>
+          <t>ChatHealthyLib</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>{"src":"FrontEndApplicationLib"}</t>
+          <t>{"src":"ChatHealthyLib"}</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/pyproject.toml</t>
+          <t>ChatHealthyLib/pyproject.toml</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/__init__.py</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/__init__.py</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/auth_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/auth_token.py</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/nonce.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/nonce.py</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/session_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/session_token.py</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/exceptions.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/exceptions.py</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/geo_extractor.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/geo_extractor.py</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/llm.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/llm.py</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/logging_service.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/logging_service.py</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/mongo_utilities.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/mongo_utilities.py</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/provider_embedding.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/provider_embedding.py</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/runtime_data_collections.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/runtime_data_collections.py</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/user/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/user/__init__.py</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_llm_facade.py</t>
+          <t>ChatHealthyLib/tests/test_llm_facade.py</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_logging_service_levels.py</t>
+          <t>ChatHealthyLib/tests/test_logging_service_levels.py</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_mongo_utilities_batch_size.py</t>
+          <t>ChatHealthyLib/tests/test_mongo_utilities_batch_size.py</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -13652,12 +13652,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib</t>
+          <t>ChatHealthyLib</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib</t>
+          <t>ChatHealthyLib</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>{"src":"FrontEndApplicationLib"}</t>
+          <t>{"src":"ChatHealthyLib"}</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
@@ -14517,7 +14517,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -14603,7 +14603,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/pyproject.toml</t>
+          <t>ChatHealthyLib/pyproject.toml</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/__init__.py</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/__init__.py</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/auth_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/auth_token.py</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/nonce.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/nonce.py</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/session_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/session_token.py</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -14904,7 +14904,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/exceptions.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/exceptions.py</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/geo_extractor.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/geo_extractor.py</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/llm.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/llm.py</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15033,7 +15033,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/logging_service.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/logging_service.py</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/mongo_utilities.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/mongo_utilities.py</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/provider_embedding.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/provider_embedding.py</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/runtime_data_collections.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/runtime_data_collections.py</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/user/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/user/__init__.py</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_llm_facade.py</t>
+          <t>ChatHealthyLib/tests/test_llm_facade.py</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_logging_service_levels.py</t>
+          <t>ChatHealthyLib/tests/test_logging_service_levels.py</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_mongo_utilities_batch_size.py</t>
+          <t>ChatHealthyLib/tests/test_mongo_utilities_batch_size.py</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -17825,12 +17825,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib</t>
+          <t>ChatHealthyLib</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib</t>
+          <t>ChatHealthyLib</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -17850,7 +17850,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>{"src":"FrontEndApplicationLib"}</t>
+          <t>{"src":"ChatHealthyLib"}</t>
         </is>
       </c>
       <c r="H400" t="inlineStr"/>
@@ -23592,7 +23592,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -23635,7 +23635,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -23678,7 +23678,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -23721,7 +23721,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/pyproject.toml</t>
+          <t>ChatHealthyLib/pyproject.toml</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -23764,7 +23764,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/__init__.py</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -23807,7 +23807,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/__init__.py</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/auth_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/auth_token.py</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/nonce.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/nonce.py</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -23936,7 +23936,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/session_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/session_token.py</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/exceptions.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/exceptions.py</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/geo_extractor.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/geo_extractor.py</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/llm.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/llm.py</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -24108,7 +24108,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/logging_service.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/logging_service.py</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -24151,7 +24151,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/mongo_utilities.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/mongo_utilities.py</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -24194,7 +24194,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/provider_embedding.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/provider_embedding.py</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -24237,7 +24237,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/runtime_data_collections.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/runtime_data_collections.py</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/user/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/user/__init__.py</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -24323,7 +24323,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_llm_facade.py</t>
+          <t>ChatHealthyLib/tests/test_llm_facade.py</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -24366,7 +24366,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_logging_service_levels.py</t>
+          <t>ChatHealthyLib/tests/test_logging_service_levels.py</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -24409,7 +24409,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_mongo_utilities_batch_size.py</t>
+          <t>ChatHealthyLib/tests/test_mongo_utilities_batch_size.py</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -26729,7 +26729,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -26772,7 +26772,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -26815,7 +26815,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/pyproject.toml</t>
+          <t>ChatHealthyLib/pyproject.toml</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -26858,7 +26858,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/__init__.py</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/__init__.py</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/auth_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/auth_token.py</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -26987,7 +26987,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/nonce.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/nonce.py</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -27030,7 +27030,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/session_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/session_token.py</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/exceptions.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/exceptions.py</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -27116,7 +27116,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/geo_extractor.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/geo_extractor.py</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -27159,7 +27159,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/llm.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/llm.py</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -27202,7 +27202,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/logging_service.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/logging_service.py</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -27245,7 +27245,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/mongo_utilities.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/mongo_utilities.py</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -27288,7 +27288,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/provider_embedding.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/provider_embedding.py</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -27331,7 +27331,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/runtime_data_collections.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/runtime_data_collections.py</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -27374,7 +27374,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/user/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/user/__init__.py</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -27417,7 +27417,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_llm_facade.py</t>
+          <t>ChatHealthyLib/tests/test_llm_facade.py</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_logging_service_levels.py</t>
+          <t>ChatHealthyLib/tests/test_logging_service_levels.py</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -27503,7 +27503,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_mongo_utilities_batch_size.py</t>
+          <t>ChatHealthyLib/tests/test_mongo_utilities_batch_size.py</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -29185,7 +29185,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-003-Manage-Errors-design-v5.docx</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -29228,7 +29228,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v10.docx</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
+          <t>ChatHealthyLib/architectureAndDesign/EPIC-003-F-005-Manage-Logging-design-v9.docx</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/pyproject.toml</t>
+          <t>ChatHealthyLib/pyproject.toml</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -29357,7 +29357,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/__init__.py</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/__init__.py</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/auth_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/auth_token.py</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -29486,7 +29486,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/nonce.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/nonce.py</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/authentication/session_token.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/authentication/session_token.py</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -29572,7 +29572,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/exceptions.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/exceptions.py</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -29615,7 +29615,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/geo_extractor.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/geo_extractor.py</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/llm.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/llm.py</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -29701,7 +29701,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/logging_service.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/logging_service.py</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -29744,7 +29744,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/mongo_utilities.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/mongo_utilities.py</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/provider_embedding.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/provider_embedding.py</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -29830,7 +29830,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/runtime_data_collections.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/runtime_data_collections.py</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -29873,7 +29873,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/user/__init__.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/user/__init__.py</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_llm_facade.py</t>
+          <t>ChatHealthyLib/tests/test_llm_facade.py</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -29959,7 +29959,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_logging_service_levels.py</t>
+          <t>ChatHealthyLib/tests/test_logging_service_levels.py</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -30002,7 +30002,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/tests/test_mongo_utilities_batch_size.py</t>
+          <t>ChatHealthyLib/tests/test_mongo_utilities_batch_size.py</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
